--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484714_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484714_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.545299999999999</v>
+        <v>7.4937</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4099</v>
+        <v>4.3583</v>
       </c>
       <c r="F2" t="n">
         <v>3.1355</v>
@@ -610,10 +610,10 @@
         <v>2.8305</v>
       </c>
       <c r="S2" t="n">
-        <v>4.0614</v>
+        <v>3.0098</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6628</v>
+        <v>1.6112</v>
       </c>
       <c r="U2" t="n">
         <v>1.3986</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0117</v>
+        <v>2.0926</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1046</v>
+        <v>0.6565</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1163</v>
+        <v>1.4362</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1596</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.502</v>
+        <v>0.5494</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3424</v>
+        <v>-1.2535</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.2258</v>
+        <v>0.976</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.2001</v>
+        <v>0.9093</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9742</v>
+        <v>0.0667</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0663</v>
+        <v>-1.6801</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6981000000000001</v>
+        <v>-0.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3682</v>
+        <v>-1.3202</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0757</v>
+        <v>-1.887</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3209</v>
+        <v>2.0757</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2278</v>
+        <v>1.6836</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8951</v>
+        <v>0.643</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3328</v>
+        <v>1.0406</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3018</v>
+        <v>0.9244</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3018</v>
+        <v>0.9244</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DAÑOBEITIA</t>
+          <t>D. CAMEROS JUAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9509</v>
+        <v>1.2473</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9509</v>
+        <v>-0.1219</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.3692</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9509</v>
+        <v>-0.1158</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9509</v>
+        <v>-0.9149</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.799</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9509</v>
+        <v>-0.207</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9509</v>
+        <v>-0.2481</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.0911</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.7579</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.2166</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.3827</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.585</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CAMEROS JUAN</t>
+          <t>J. ARTIGUES DAÑOBEITIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8496</v>
+        <v>0.9509</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4931</v>
+        <v>0.9509</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3427</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1158</v>
+        <v>0.9509</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9149</v>
+        <v>0.9509</v>
       </c>
       <c r="I5" t="n">
-        <v>0.799</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.207</v>
+        <v>0.9509</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2481</v>
+        <v>0.9509</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0411</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0911</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6667999999999999</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7579</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.997</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5879</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4091</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.585</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>J. GIL SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8264</v>
+        <v>0.2714</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6891</v>
+        <v>0.0974</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5155</v>
+        <v>0.174</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7040999999999999</v>
+        <v>0.1299</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5494</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2535</v>
+        <v>0.1299</v>
       </c>
       <c r="J6" t="n">
-        <v>0.976</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9093</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6801</v>
+        <v>0.1299</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.36</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3202</v>
+        <v>0.1299</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4174</v>
+        <v>0.1415</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7026</v>
+        <v>0.0974</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1199</v>
+        <v>0.0441</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GIL SANCHEZ</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1475</v>
+        <v>0.223</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-1.761</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1475</v>
+        <v>1.984</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1299</v>
+        <v>-0.1596</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-2.502</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1299</v>
+        <v>2.3424</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-1.2258</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-3.2001</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.9742</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1299</v>
+        <v>1.0663</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1299</v>
+        <v>0.3682</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0176</v>
+        <v>1.4392</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.2387</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0176</v>
+        <v>0.2005</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. CORONA NAVARRO</t>
+          <t>I. HORRACH SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0322</v>
+        <v>-0.1351</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0348</v>
+        <v>-0.4402</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0026</v>
+        <v>0.3051</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.1138</v>
+        <v>0.2234</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1582</v>
+        <v>-0.1448</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.2721</v>
+        <v>0.3682</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.4191</v>
+        <v>0.3592</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4853</v>
+        <v>0.3592</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.9044</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6947</v>
+        <v>-0.1358</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3271</v>
+        <v>-0.504</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3676</v>
+        <v>0.3682</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0757</v>
+        <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2138</v>
+        <v>-0.6604</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4225</v>
+        <v>-0.1579</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7913</v>
+        <v>-0.5026</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3208</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8488</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. HORRACH SANCHEZ</t>
+          <t>R. CORONA NAVARRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4417</v>
+        <v>-0.492</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6939</v>
+        <v>-1.1507</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2522</v>
+        <v>0.6587</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2234</v>
+        <v>-3.1138</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1448</v>
+        <v>1.1582</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3682</v>
+        <v>-4.2721</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3592</v>
+        <v>-2.4191</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3592</v>
+        <v>1.4853</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-3.9044</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1358</v>
+        <v>-0.6947</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.504</v>
+        <v>-0.3271</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3682</v>
+        <v>-0.3676</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9435</v>
+        <v>0.1887</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9435</v>
+        <v>2.0757</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.967</v>
+        <v>2.7539</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4115</v>
+        <v>1.3066</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5555</v>
+        <v>1.4474</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.3208</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.8488</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6328</v>
+        <v>-0.9164</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0465</v>
+        <v>-2.3829</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4136</v>
+        <v>1.4666</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2835</v>
@@ -1234,13 +1234,13 @@
         <v>2.8305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1041</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1706</v>
+        <v>0.493</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0665</v>
+        <v>0.1194</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9492</v>
+        <v>-2.0206</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2077</v>
+        <v>-4.2262</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2586</v>
+        <v>2.2057</v>
       </c>
       <c r="G11" t="n">
         <v>1.4486</v>
@@ -1312,13 +1312,13 @@
         <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1875</v>
+        <v>0.1161</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0617</v>
+        <v>0.0432</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1259</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1744</v>
+        <v>-2.5936</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.094</v>
+        <v>-2.6455</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0804</v>
+        <v>0.0519</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5958</v>
@@ -1390,13 +1390,13 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4779</v>
+        <v>1.0587</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0029</v>
+        <v>0.4514</v>
       </c>
       <c r="U12" t="n">
-        <v>0.475</v>
+        <v>0.6073</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8678</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.6968</v>
+        <v>-5.5411</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4719</v>
+        <v>-1.6336</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.2249</v>
+        <v>-3.9075</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7814</v>
@@ -1468,13 +1468,13 @@
         <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>0.08459999999999999</v>
+        <v>1.2403</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0559</v>
+        <v>0.7824</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1405</v>
+        <v>0.458</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4904</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5957000000000008</v>
+        <v>0.5800999999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.474799999999998</v>
+        <v>-8.2989</v>
       </c>
       <c r="F14" t="n">
-        <v>8.879200000000001</v>
+        <v>8.879399999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.139799999999999</v>
+        <v>-6.139800000000001</v>
       </c>
       <c r="H14" t="n">
         <v>-0.7279999999999998</v>
@@ -1519,7 +1519,7 @@
         <v>-5.4123</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.2298</v>
+        <v>-1.229800000000001</v>
       </c>
       <c r="K14" t="n">
         <v>2.1283</v>
@@ -1546,13 +1546,13 @@
         <v>17.9265</v>
       </c>
       <c r="S14" t="n">
-        <v>9.619899999999999</v>
+        <v>10.7958</v>
       </c>
       <c r="T14" t="n">
-        <v>5.116499999999999</v>
+        <v>6.2924</v>
       </c>
       <c r="U14" t="n">
-        <v>4.5035</v>
+        <v>4.503500000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2452</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8777</v>
+        <v>3.6378</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4458</v>
+        <v>1.8356</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4319</v>
+        <v>1.8023</v>
       </c>
       <c r="G15" t="n">
         <v>0.9076</v>
@@ -1624,13 +1624,13 @@
         <v>2.4531</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0298</v>
+        <v>-1.2697</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7396</v>
+        <v>-0.3498</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2903</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>2.4904</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0394</v>
+        <v>1.9058</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5587</v>
+        <v>0.2664</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4807</v>
+        <v>1.6394</v>
       </c>
       <c r="G16" t="n">
         <v>1.6004</v>
@@ -1702,13 +1702,13 @@
         <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7688</v>
+        <v>-1.9024</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5726</v>
+        <v>-0.8649</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1962</v>
+        <v>-1.0375</v>
       </c>
       <c r="V16" t="n">
         <v>0.3208</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. DE YRAOLAGOTIA TELLO</t>
+          <t>A. GARCIA RUIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8326</v>
+        <v>1.8011</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7349</v>
+        <v>-0.5637</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5675</v>
+        <v>2.3648</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4217</v>
+        <v>3.2514</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9814000000000001</v>
+        <v>0.8789</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4031</v>
+        <v>2.3725</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1822</v>
+        <v>2.0837</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1909</v>
+        <v>1.4001</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9913</v>
+        <v>0.6836</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7605</v>
+        <v>1.1677</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1723</v>
+        <v>-0.5212</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4118</v>
+        <v>1.6889</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6983</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R17" t="n">
-        <v>3.5853</v>
+        <v>1.1322</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8911</v>
+        <v>-0.3935</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.6337</v>
+        <v>-0.4395</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2573</v>
+        <v>0.0459</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6036</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6036</v>
+        <v>0.6226</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARCIA RUIZ</t>
+          <t>J. DE YRAOLAGOTIA TELLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6327</v>
+        <v>1.4455</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7585</v>
+        <v>-0.54</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3912</v>
+        <v>1.9855</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2514</v>
+        <v>1.4217</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8789</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3725</v>
+        <v>2.4031</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0837</v>
+        <v>2.1822</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4001</v>
+        <v>0.1909</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6836</v>
+        <v>1.9913</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1677</v>
+        <v>-0.7605</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5212</v>
+        <v>-1.1723</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6889</v>
+        <v>0.4118</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.6983</v>
+        <v>1.6983</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1322</v>
+        <v>3.5853</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-2.2782</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6343</v>
+        <v>-1.4388</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07240000000000001</v>
+        <v>-0.8393</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6036</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6226</v>
+        <v>0.6036</v>
       </c>
       <c r="X18" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5475</v>
+        <v>0.954</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.7881</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0458</v>
+        <v>0.1658</v>
       </c>
       <c r="G19" t="n">
         <v>1.1171</v>
@@ -1936,13 +1936,13 @@
         <v>3.5853</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.8904</v>
+        <v>-2.4839</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5873</v>
+        <v>-1.3924</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3032</v>
+        <v>-1.0915</v>
       </c>
       <c r="V19" t="n">
         <v>1.566</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CALERO SEVILLANO</t>
+          <t>J. GONZALEZ LÓPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3864</v>
+        <v>0.317</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8213</v>
+        <v>0.317</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2077</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4139</v>
+        <v>0.317</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0158</v>
+        <v>0.317</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6019</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1096</v>
+        <v>0.317</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4492</v>
+        <v>0.317</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5588</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5235</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5666</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0431</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5096</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.774</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2644</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2369</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5719</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.335</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LÓPEZ</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.317</v>
+        <v>-0.123</v>
       </c>
       <c r="E21" t="n">
-        <v>0.317</v>
+        <v>-0.4064</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.2834</v>
       </c>
       <c r="G21" t="n">
-        <v>0.317</v>
+        <v>-0.0407</v>
       </c>
       <c r="H21" t="n">
-        <v>0.317</v>
+        <v>0.979</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-1.0197</v>
       </c>
       <c r="J21" t="n">
-        <v>0.317</v>
+        <v>-0.5873</v>
       </c>
       <c r="K21" t="n">
-        <v>0.317</v>
+        <v>0.0211</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.5466</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.9579</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.4113</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-0.0448</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.1809</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0.2257</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. LOPEZ RICO</t>
+          <t>J. CALERO SEVILLANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1788</v>
+        <v>-0.2511</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0168</v>
+        <v>-1.4059</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.162</v>
+        <v>1.1548</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1051</v>
+        <v>0.4139</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4015</v>
+        <v>1.0158</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5066000000000001</v>
+        <v>-0.6019</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0296</v>
+        <v>-0.1096</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6284</v>
+        <v>0.4492</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6581</v>
+        <v>-0.5588</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0755</v>
+        <v>0.5235</v>
       </c>
       <c r="N22" t="n">
-        <v>0.227</v>
+        <v>0.5666</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1515</v>
+        <v>-0.0431</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1887</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1887</v>
+        <v>2.2644</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4726</v>
+        <v>-0.4006</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0465</v>
+        <v>-0.0127</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4262</v>
+        <v>-0.3879</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.4904</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>M. LOPEZ RICO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2205</v>
+        <v>-0.2846</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5038</v>
+        <v>-0.0168</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2834</v>
+        <v>-0.2678</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0407</v>
+        <v>0.1051</v>
       </c>
       <c r="H23" t="n">
-        <v>0.979</v>
+        <v>-0.4015</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0197</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5873</v>
+        <v>0.0296</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0211</v>
+        <v>-0.6284</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.6581</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5466</v>
+        <v>0.0755</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9579</v>
+        <v>0.227</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4113</v>
+        <v>-0.1515</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1422</v>
+        <v>-0.5784</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0835</v>
+        <v>-0.0465</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2257</v>
+        <v>-0.532</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3952</v>
+        <v>-1.6082</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8232</v>
+        <v>-1.1155</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.4927</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6908</v>
@@ -2326,13 +2326,13 @@
         <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4085</v>
+        <v>0.1956</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3092</v>
+        <v>0.0169</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0994</v>
+        <v>0.1787</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2452</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0232</v>
+        <v>-2.0664</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6172</v>
+        <v>-2.4223</v>
       </c>
       <c r="F25" t="n">
-        <v>0.594</v>
+        <v>0.3559</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4422</v>
@@ -2404,13 +2404,13 @@
         <v>1.1322</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0982</v>
+        <v>0.055</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.164</v>
+        <v>0.0308</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2622</v>
+        <v>0.0241</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9244</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.2199</v>
+        <v>-5.1322</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.5183</v>
+        <v>-5.6157</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2984</v>
+        <v>0.4836</v>
       </c>
       <c r="G26" t="n">
         <v>-0.8206</v>
@@ -2482,13 +2482,13 @@
         <v>2.8305</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6067</v>
+        <v>-0.5189</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.09</v>
+        <v>-0.1874</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5167</v>
+        <v>-0.3315</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8491</v>
@@ -2515,25 +2515,25 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5957000000000017</v>
+        <v>0.5956999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-8.879300000000001</v>
+        <v>-8.879200000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>9.474899999999998</v>
+        <v>9.475000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>6.139900000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7279000000000001</v>
+        <v>0.7279000000000003</v>
       </c>
       <c r="I27" t="n">
-        <v>5.412199999999999</v>
+        <v>5.4122</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9101</v>
+        <v>4.910100000000001</v>
       </c>
       <c r="K27" t="n">
         <v>2.8564</v>
@@ -2545,7 +2545,7 @@
         <v>1.2299</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.128299999999999</v>
+        <v>-2.1283</v>
       </c>
       <c r="O27" t="n">
         <v>3.3582</v>
@@ -2557,16 +2557,16 @@
         <v>-17.9265</v>
       </c>
       <c r="R27" t="n">
-        <v>20.757</v>
+        <v>20.75700000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>-9.620000000000001</v>
+        <v>-9.6198</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.503399999999999</v>
+        <v>-4.5034</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.116599999999999</v>
+        <v>-5.1166</v>
       </c>
       <c r="V27" t="n">
         <v>1.2453</v>
